--- a/data/flood_data.xlsx
+++ b/data/flood_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UET\Research\Supervision\Students\Bachelors_Students\Batch5\1.zohaib_naqeeb\implementation\Laeeq\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UET\PycharmProjects\RiverStreamflowPrediction\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984D200A-0592-41AB-B5BC-B0EBCBF5B954}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC05EC6-8B08-481F-966B-D189F447356B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25413,14 +25413,14 @@
         <v>42060</v>
       </c>
       <c r="B1153" s="9">
-        <v>15.4</v>
+        <v>16</v>
       </c>
       <c r="C1153" s="56">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D1153" s="26">
         <f t="shared" si="17"/>
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="E1153" s="18">
         <v>28.3</v>
